--- a/exceldoc/ESTRATEGIA REQUISITOS.xlsx
+++ b/exceldoc/ESTRATEGIA REQUISITOS.xlsx
@@ -72,7 +72,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="41">
     <border/>
     <border>
       <left style="thin">
@@ -471,11 +471,29 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -701,6 +719,20 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5090,16 +5122,46 @@
       <c r="AA65" s="23" t="n"/>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="55">
-      <c r="A66" s="54" t="n"/>
-      <c r="B66" s="54" t="n"/>
-      <c r="C66" s="23" t="n"/>
-      <c r="D66" s="54" t="n"/>
-      <c r="E66" s="23" t="n"/>
-      <c r="F66" s="23" t="n"/>
-      <c r="G66" s="23" t="n"/>
-      <c r="H66" s="23" t="n"/>
-      <c r="I66" s="23" t="n"/>
-      <c r="J66" s="23" t="n"/>
+      <c r="A66" s="85" t="inlineStr">
+        <is>
+          <t>Desarrollar el Módulo de Seguimiento Diario de la App Móvil: recuperación de contraseña, foto de perfil, tema y notificaciones push</t>
+        </is>
+      </c>
+      <c r="B66" s="85" t="inlineStr">
+        <is>
+          <t>SEGUIMIENTO DIARIO (APP MÓVIL)</t>
+        </is>
+      </c>
+      <c r="C66" s="85" t="inlineStr">
+        <is>
+          <t>Create (Crear, Registrar)</t>
+        </is>
+      </c>
+      <c r="D66" s="86" t="inlineStr">
+        <is>
+          <t>HU64</t>
+        </is>
+      </c>
+      <c r="E66" s="87" t="inlineStr">
+        <is>
+          <t>Como Afiliado, quiero recuperar mi contraseña solicitando un enlace de restablecimiento, para volver a acceder a la app si la olvido.</t>
+        </is>
+      </c>
+      <c r="F66" s="88" t="b">
+        <v>0</v>
+      </c>
+      <c r="G66" s="88" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" s="88" t="b">
+        <v>1</v>
+      </c>
+      <c r="I66" s="88" t="b">
+        <v>0</v>
+      </c>
+      <c r="J66" s="88" t="b">
+        <v>1</v>
+      </c>
       <c r="K66" s="23" t="n"/>
       <c r="L66" s="23" t="n"/>
       <c r="M66" s="23" t="n"/>
@@ -5119,16 +5181,38 @@
       <c r="AA66" s="23" t="n"/>
     </row>
     <row r="67" ht="15.75" customHeight="1" s="55">
-      <c r="A67" s="54" t="n"/>
-      <c r="B67" s="54" t="n"/>
-      <c r="C67" s="23" t="n"/>
-      <c r="D67" s="54" t="n"/>
-      <c r="E67" s="23" t="n"/>
-      <c r="F67" s="23" t="n"/>
-      <c r="G67" s="23" t="n"/>
-      <c r="H67" s="23" t="n"/>
-      <c r="I67" s="23" t="n"/>
-      <c r="J67" s="23" t="n"/>
+      <c r="A67" s="89" t="n"/>
+      <c r="B67" s="89" t="n"/>
+      <c r="C67" s="85" t="inlineStr">
+        <is>
+          <t>Update (Actualizar, Editar)</t>
+        </is>
+      </c>
+      <c r="D67" s="86" t="inlineStr">
+        <is>
+          <t>HU65</t>
+        </is>
+      </c>
+      <c r="E67" s="87" t="inlineStr">
+        <is>
+          <t>Como Afiliado, quiero subir una foto de perfil desde la app móvil, para personalizar mi cuenta.</t>
+        </is>
+      </c>
+      <c r="F67" s="88" t="b">
+        <v>0</v>
+      </c>
+      <c r="G67" s="88" t="b">
+        <v>0</v>
+      </c>
+      <c r="H67" s="88" t="b">
+        <v>1</v>
+      </c>
+      <c r="I67" s="88" t="b">
+        <v>0</v>
+      </c>
+      <c r="J67" s="88" t="b">
+        <v>1</v>
+      </c>
       <c r="K67" s="23" t="n"/>
       <c r="L67" s="23" t="n"/>
       <c r="M67" s="23" t="n"/>
@@ -5148,16 +5232,38 @@
       <c r="AA67" s="23" t="n"/>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="55">
-      <c r="A68" s="54" t="n"/>
-      <c r="B68" s="54" t="n"/>
-      <c r="C68" s="23" t="n"/>
-      <c r="D68" s="54" t="n"/>
-      <c r="E68" s="23" t="n"/>
-      <c r="F68" s="23" t="n"/>
-      <c r="G68" s="23" t="n"/>
-      <c r="H68" s="23" t="n"/>
-      <c r="I68" s="23" t="n"/>
-      <c r="J68" s="23" t="n"/>
+      <c r="A68" s="89" t="n"/>
+      <c r="B68" s="89" t="n"/>
+      <c r="C68" s="85" t="inlineStr">
+        <is>
+          <t>Update (Actualizar, Editar)</t>
+        </is>
+      </c>
+      <c r="D68" s="86" t="inlineStr">
+        <is>
+          <t>HU66</t>
+        </is>
+      </c>
+      <c r="E68" s="87" t="inlineStr">
+        <is>
+          <t>Como Afiliado, quiero cambiar el tema de la app móvil entre claro y oscuro, para personalizar la interfaz.</t>
+        </is>
+      </c>
+      <c r="F68" s="88" t="b">
+        <v>0</v>
+      </c>
+      <c r="G68" s="88" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" s="88" t="b">
+        <v>1</v>
+      </c>
+      <c r="I68" s="88" t="b">
+        <v>0</v>
+      </c>
+      <c r="J68" s="88" t="b">
+        <v>1</v>
+      </c>
       <c r="K68" s="23" t="n"/>
       <c r="L68" s="23" t="n"/>
       <c r="M68" s="23" t="n"/>
@@ -5177,16 +5283,38 @@
       <c r="AA68" s="23" t="n"/>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="55">
-      <c r="A69" s="54" t="n"/>
-      <c r="B69" s="54" t="n"/>
-      <c r="C69" s="23" t="n"/>
-      <c r="D69" s="54" t="n"/>
-      <c r="E69" s="23" t="n"/>
-      <c r="F69" s="23" t="n"/>
-      <c r="G69" s="23" t="n"/>
-      <c r="H69" s="23" t="n"/>
-      <c r="I69" s="23" t="n"/>
-      <c r="J69" s="23" t="n"/>
+      <c r="A69" s="90" t="n"/>
+      <c r="B69" s="90" t="n"/>
+      <c r="C69" s="85" t="inlineStr">
+        <is>
+          <t>Create (Crear, Registrar)</t>
+        </is>
+      </c>
+      <c r="D69" s="86" t="inlineStr">
+        <is>
+          <t>HU67</t>
+        </is>
+      </c>
+      <c r="E69" s="87" t="inlineStr">
+        <is>
+          <t>Como Afiliado, quiero recibir notificaciones push de la app móvil, para estar al tanto de mi rutina y nutrición.</t>
+        </is>
+      </c>
+      <c r="F69" s="88" t="b">
+        <v>0</v>
+      </c>
+      <c r="G69" s="88" t="b">
+        <v>0</v>
+      </c>
+      <c r="H69" s="88" t="b">
+        <v>1</v>
+      </c>
+      <c r="I69" s="88" t="b">
+        <v>0</v>
+      </c>
+      <c r="J69" s="88" t="b">
+        <v>1</v>
+      </c>
       <c r="K69" s="23" t="n"/>
       <c r="L69" s="23" t="n"/>
       <c r="M69" s="23" t="n"/>
@@ -32379,7 +32507,8 @@
       <c r="AA1006" s="23" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="46">
+    <mergeCell ref="B66:B69"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="B6:B10"/>
     <mergeCell ref="E1:E2"/>
@@ -32390,13 +32519,14 @@
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="A27:A37"/>
     <mergeCell ref="S1:V1"/>
+    <mergeCell ref="A66:A69"/>
     <mergeCell ref="A56:A57"/>
     <mergeCell ref="B11:B16"/>
     <mergeCell ref="B51:B55"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="B3:B5"/>
+    <mergeCell ref="A60"/>
     <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A60"/>
     <mergeCell ref="L1:L2"/>
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="A61:A65"/>
